--- a/master_vehicles_tracker.xlsx
+++ b/master_vehicles_tracker.xlsx
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Real-time status across Generation, Editing, and Uploading | Last updated: 2026-09-17 03:52:52</t>
+          <t>Real-time status across Generation, Editing, and Uploading | Last updated: 2026-09-19 03:52:36</t>
         </is>
       </c>
     </row>
@@ -636,12 +636,12 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>90 (180%)</t>
+          <t>95 (190%)</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>91 (182%)</t>
+          <t>96 (192%)</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">

--- a/master_vehicles_tracker.xlsx
+++ b/master_vehicles_tracker.xlsx
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Real-time status across Generation, Editing, and Uploading | Last updated: 2026-09-19 03:52:36</t>
+          <t>Real-time status across Generation, Editing, and Uploading | Last updated: 2026-09-20 01:01:45</t>
         </is>
       </c>
     </row>
@@ -636,12 +636,12 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>95 (190%)</t>
+          <t>98 (196%)</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>96 (192%)</t>
+          <t>99 (198%)</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">

--- a/master_vehicles_tracker.xlsx
+++ b/master_vehicles_tracker.xlsx
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Real-time status across Generation, Editing, and Uploading | Last updated: 2026-09-20 01:01:45</t>
+          <t>Real-time status across Generation, Editing, and Uploading | Last updated: 2026-09-20 01:19:27</t>
         </is>
       </c>
     </row>

--- a/master_vehicles_tracker.xlsx
+++ b/master_vehicles_tracker.xlsx
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Real-time status across Generation, Editing, and Uploading | Last updated: 2026-09-20 01:19:27</t>
+          <t>Real-time status across Generation, Editing, and Uploading | Last updated: 2026-09-20 01:21:14</t>
         </is>
       </c>
     </row>

--- a/master_vehicles_tracker.xlsx
+++ b/master_vehicles_tracker.xlsx
@@ -573,7 +573,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="69" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Real-time status across Generation, Editing, and Uploading | Last updated: 2026-09-20 01:21:14</t>
+          <t>Real-time status across Generation, Editing, and Uploading | Last updated: 2026-09-21 00:30:23</t>
         </is>
       </c>
     </row>
@@ -636,12 +636,12 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>98 (196%)</t>
+          <t>100 (200%)</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>99 (198%)</t>
+          <t>101 (202%)</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">

--- a/master_vehicles_tracker.xlsx
+++ b/master_vehicles_tracker.xlsx
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Real-time status across Generation, Editing, and Uploading | Last updated: 2026-09-21 00:30:23</t>
+          <t>Real-time status across Generation, Editing, and Uploading | Last updated: 2026-09-23 18:06:22</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>output\100_popular_cars_in_India_03_Maruti_Suzuki_Wagon_R\Maruti_Suzuki_Wagon_R.mp4</t>
+          <t>output\Popular_Cars_USA_Canada_Top_50_03_Toyota_RAV4\Toyota_RAV4.mp4</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
